--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202605/Category_P&L_20260504.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2026/202605/Category_P&L_20260504.xlsx
@@ -42523,28 +42523,28 @@
         <v>46141</v>
       </c>
       <c r="B1109">
-        <v>91094854.09</v>
+        <v>91593172.23</v>
       </c>
       <c r="C1109">
-        <v>-553460.4300000001</v>
+        <v>638525.74</v>
       </c>
       <c r="D1109">
-        <v>-0.006076</v>
+        <v>0.007009</v>
       </c>
       <c r="E1109">
-        <v>-9727.09</v>
+        <v>-99657.87</v>
       </c>
       <c r="F1109">
-        <v>-0.000107</v>
+        <v>-0.001094</v>
       </c>
       <c r="G1109">
-        <v>-90311.41</v>
+        <v>-25267.2</v>
       </c>
       <c r="H1109">
-        <v>-0.0009909999999999999</v>
+        <v>-0.000277</v>
       </c>
       <c r="I1109">
-        <v>-2.64</v>
+        <v>-7.92</v>
       </c>
       <c r="J1109">
         <v>0</v>
@@ -42561,28 +42561,28 @@
         <v>46142</v>
       </c>
       <c r="B1110">
-        <v>91094854.09</v>
+        <v>92671718.28</v>
       </c>
       <c r="C1110">
-        <v>-553460.4300000001</v>
+        <v>915883.26</v>
       </c>
       <c r="D1110">
-        <v>-0.006076</v>
+        <v>0.009998999999999999</v>
       </c>
       <c r="E1110">
-        <v>-9727.09</v>
+        <v>69294.63</v>
       </c>
       <c r="F1110">
-        <v>-0.000107</v>
+        <v>0.000757</v>
       </c>
       <c r="G1110">
-        <v>-90311.41</v>
+        <v>111835.98</v>
       </c>
       <c r="H1110">
-        <v>-0.0009909999999999999</v>
+        <v>0.001221</v>
       </c>
       <c r="I1110">
-        <v>-2.64</v>
+        <v>45.21</v>
       </c>
       <c r="J1110">
         <v>0</v>
@@ -42599,28 +42599,28 @@
         <v>46143</v>
       </c>
       <c r="B1111">
-        <v>92552592.2</v>
+        <v>92433893.81999999</v>
       </c>
       <c r="C1111">
-        <v>284113.15</v>
+        <v>-144722.92</v>
       </c>
       <c r="D1111">
-        <v>0.003119</v>
+        <v>-0.001562</v>
       </c>
       <c r="E1111">
-        <v>-72525.66</v>
+        <v>-179725.11</v>
       </c>
       <c r="F1111">
-        <v>-0.000796</v>
+        <v>-0.001939</v>
       </c>
       <c r="G1111">
-        <v>-51320.68</v>
+        <v>-28580.98</v>
       </c>
       <c r="H1111">
-        <v>-0.000563</v>
+        <v>-0.000308</v>
       </c>
       <c r="I1111">
-        <v>0</v>
+        <v>-6.27</v>
       </c>
       <c r="J1111">
         <v>0</v>
@@ -42637,19 +42637,19 @@
         <v>46146</v>
       </c>
       <c r="B1112">
-        <v>92552592.2</v>
+        <v>92552688.8</v>
       </c>
       <c r="C1112">
         <v>284113.15</v>
       </c>
       <c r="D1112">
-        <v>0.00307</v>
+        <v>0.003074</v>
       </c>
       <c r="E1112">
         <v>-72525.66</v>
       </c>
       <c r="F1112">
-        <v>-0.000784</v>
+        <v>-0.000785</v>
       </c>
       <c r="G1112">
         <v>-51320.68</v>
